--- a/workspace/framework_paper/map-bf/map-bf-10/map-bf-10_times.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-10/map-bf-10_times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>bf</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bf-seq</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -478,6 +483,9 @@
       <c r="H2" t="n">
         <v>1.894676554203033</v>
       </c>
+      <c r="I2" t="n">
+        <v>9.126702718734741</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -504,6 +512,9 @@
       <c r="H3" t="n">
         <v>2.115987896323204</v>
       </c>
+      <c r="I3" t="n">
+        <v>23.87136682271957</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -530,6 +541,9 @@
       <c r="H4" t="n">
         <v>2.168079690933228</v>
       </c>
+      <c r="I4" t="n">
+        <v>13.8283218640089</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -556,6 +570,9 @@
       <c r="H5" t="n">
         <v>1.500013507008553</v>
       </c>
+      <c r="I5" t="n">
+        <v>11.00256102621555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -582,6 +599,9 @@
       <c r="H6" t="n">
         <v>1.554190745949745</v>
       </c>
+      <c r="I6" t="n">
+        <v>19.46603390321135</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -608,6 +628,9 @@
       <c r="H7" t="n">
         <v>1.523443705439568</v>
       </c>
+      <c r="I7" t="n">
+        <v>13.9417960101366</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -634,6 +657,9 @@
       <c r="H8" t="n">
         <v>1.281998206973076</v>
       </c>
+      <c r="I8" t="n">
+        <v>13.78581556379795</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -660,6 +686,9 @@
       <c r="H9" t="n">
         <v>0.9347695159912109</v>
       </c>
+      <c r="I9" t="n">
+        <v>7.446025257110596</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -686,6 +715,9 @@
       <c r="H10" t="n">
         <v>0.5103531855344773</v>
       </c>
+      <c r="I10" t="n">
+        <v>1.399673088490963</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -712,6 +744,9 @@
       <c r="H11" t="n">
         <v>0.6885533022880554</v>
       </c>
+      <c r="I11" t="n">
+        <v>11.26953111350536</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -738,6 +773,9 @@
       <c r="H12" t="n">
         <v>0.5082145029306412</v>
       </c>
+      <c r="I12" t="n">
+        <v>1.749042750895023</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -764,6 +802,9 @@
       <c r="H13" t="n">
         <v>0.5218579131364822</v>
       </c>
+      <c r="I13" t="n">
+        <v>1.639211337864399</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -790,6 +831,9 @@
       <c r="H14" t="n">
         <v>0.4717095106840133</v>
       </c>
+      <c r="I14" t="n">
+        <v>1.007412556409836</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -816,6 +860,9 @@
       <c r="H15" t="n">
         <v>0.3987211972475052</v>
       </c>
+      <c r="I15" t="n">
+        <v>1.390571956336498</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -842,6 +889,9 @@
       <c r="H16" t="n">
         <v>0.401238557100296</v>
       </c>
+      <c r="I16" t="n">
+        <v>1.338605097085237</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -868,6 +918,9 @@
       <c r="H17" t="n">
         <v>3.738481622338295</v>
       </c>
+      <c r="I17" t="n">
+        <v>18.31381565928459</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -894,6 +947,9 @@
       <c r="H18" t="n">
         <v>5.208695892095566</v>
       </c>
+      <c r="I18" t="n">
+        <v>57.62197496920824</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -920,6 +976,9 @@
       <c r="H19" t="n">
         <v>3.866872380971909</v>
       </c>
+      <c r="I19" t="n">
+        <v>25.23952328801155</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -946,6 +1005,9 @@
       <c r="H20" t="n">
         <v>4.450704863667488</v>
       </c>
+      <c r="I20" t="n">
+        <v>58.68308430731297</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -971,6 +1033,9 @@
       </c>
       <c r="H21" t="n">
         <v>5.764198301434517</v>
+      </c>
+      <c r="I21" t="n">
+        <v>57.1345209312439</v>
       </c>
     </row>
   </sheetData>
